--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484136_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484136_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9921</v>
+        <v>7.2798</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4527</v>
+        <v>4.2434</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5394</v>
+        <v>3.0364</v>
       </c>
       <c r="G2" t="n">
-        <v>2.433</v>
+        <v>3.8873</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3487</v>
+        <v>2.0308</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0843</v>
+        <v>1.8565</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3793</v>
+        <v>3.5138</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1785</v>
+        <v>2.344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2008</v>
+        <v>1.1698</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0537</v>
+        <v>0.3735</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1702</v>
+        <v>-0.3132</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1165</v>
+        <v>0.6867</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7693</v>
+        <v>0.9876</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6642</v>
+        <v>0.3005</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1051</v>
+        <v>0.6872</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.8097</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4012</v>
+        <v>2.4129</v>
       </c>
       <c r="X2" t="n">
         <v>-0.6032</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.924</v>
+        <v>6.2435</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6912</v>
+        <v>3.9846</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2328</v>
+        <v>2.2589</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8873</v>
+        <v>2.433</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0308</v>
+        <v>2.3487</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8565</v>
+        <v>0.0843</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5138</v>
+        <v>2.3793</v>
       </c>
       <c r="K3" t="n">
-        <v>2.344</v>
+        <v>2.1785</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1698</v>
+        <v>0.2008</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3735</v>
+        <v>0.0537</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3132</v>
+        <v>0.1702</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6867</v>
+        <v>-0.1165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6318</v>
+        <v>2.0207</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7483</v>
+        <v>1.1961</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8835</v>
+        <v>0.8246</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8097</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4129</v>
+        <v>1.4012</v>
       </c>
       <c r="X3" t="n">
         <v>-0.6032</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0153</v>
+        <v>5.7069</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3297</v>
+        <v>4.4907</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6856</v>
+        <v>1.2162</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8476</v>
+        <v>5.9403</v>
       </c>
       <c r="H4" t="n">
+        <v>2.0913</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.849</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.2308</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.5308</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.2905</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.4395</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.5871</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.2606</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.2021</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.0363</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1658</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6455</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.4493</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0948</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9919</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.4293</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8616</v>
+        <v>0.2438</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0481</v>
+        <v>0.1855</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4177</v>
+        <v>5.13</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5101</v>
+        <v>3.0236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9076</v>
+        <v>2.1064</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9403</v>
+        <v>2.8476</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0913</v>
+        <v>1.5871</v>
       </c>
       <c r="I5" t="n">
-        <v>3.849</v>
+        <v>1.2606</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2308</v>
+        <v>2.2021</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5308</v>
+        <v>2.0363</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7</v>
+        <v>0.1658</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2905</v>
+        <v>0.6455</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4395</v>
+        <v>-0.4493</v>
       </c>
       <c r="O5" t="n">
-        <v>0.149</v>
+        <v>1.0948</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8599</v>
+        <v>1.0245</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7368</v>
+        <v>0.5555</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1231</v>
+        <v>0.469</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9614</v>
+        <v>4.9357</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1313</v>
+        <v>0.787</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0927</v>
+        <v>4.1488</v>
       </c>
       <c r="G6" t="n">
         <v>3.8771</v>
@@ -922,13 +922,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6155</v>
+        <v>1.5898</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8105</v>
+        <v>0.1078</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4259</v>
+        <v>1.4821</v>
       </c>
       <c r="V6" t="n">
         <v>0.4607</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7964</v>
+        <v>3.4327</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4404</v>
+        <v>1.217</v>
       </c>
       <c r="F7" t="n">
-        <v>2.356</v>
+        <v>2.2157</v>
       </c>
       <c r="G7" t="n">
         <v>0.8098</v>
@@ -1000,13 +1000,13 @@
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6717</v>
+        <v>-0.0354</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7368</v>
+        <v>0.0398</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.0752</v>
       </c>
       <c r="V7" t="n">
         <v>0.6745</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7187</v>
+        <v>0.8799</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9705</v>
+        <v>0.5143</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6893</v>
+        <v>0.3655</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6062</v>
+        <v>2.4599</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0985</v>
+        <v>0.7912</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5077</v>
+        <v>1.6687</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1558</v>
+        <v>4.1763</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3413</v>
+        <v>2.2485</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1855</v>
+        <v>1.9278</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4504</v>
+        <v>-1.7164</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2428</v>
+        <v>-1.4573</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6932</v>
+        <v>-0.2591</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.7693</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.9596</v>
+        <v>-3.9677</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2786</v>
+        <v>0.6022</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2301</v>
+        <v>0.0398</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0485</v>
+        <v>0.5625</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4119</v>
+        <v>0.4892</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2622</v>
+        <v>-2.4807</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6741</v>
+        <v>2.9698</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4599</v>
+        <v>1.6062</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7912</v>
+        <v>1.0985</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6687</v>
+        <v>0.5077</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1763</v>
+        <v>1.1558</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2485</v>
+        <v>1.3413</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9278</v>
+        <v>-0.1855</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7164</v>
+        <v>0.4504</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4573</v>
+        <v>-0.2428</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2591</v>
+        <v>0.6932</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1822</v>
+        <v>-3.7693</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9677</v>
+        <v>-4.9596</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1343</v>
+        <v>2.049</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7368</v>
+        <v>0.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8711</v>
+        <v>1.3291</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1788</v>
+        <v>-0.2885</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0853</v>
+        <v>-0.2208</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2642</v>
+        <v>-0.0678</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3944</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6241</v>
+        <v>0.5144</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4308</v>
+        <v>0.1247</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1933</v>
+        <v>0.3897</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4085</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3789</v>
+        <v>-0.8176</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.129</v>
+        <v>-2.2311</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7501</v>
+        <v>1.4135</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2399</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3172</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1191</v>
+        <v>0.0171</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1981</v>
+        <v>0.8615</v>
       </c>
       <c r="V11" t="n">
         <v>-0.266</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>32.67979999999999</v>
+        <v>32.9916</v>
       </c>
       <c r="E12" t="n">
-        <v>13.0164</v>
+        <v>13.328</v>
       </c>
       <c r="F12" t="n">
         <v>19.6634</v>
@@ -1390,13 +1390,13 @@
         <v>13.8868</v>
       </c>
       <c r="S12" t="n">
-        <v>9.748999999999999</v>
+        <v>10.0606</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0332</v>
+        <v>3.3451</v>
       </c>
       <c r="U12" t="n">
-        <v>6.715599999999999</v>
+        <v>6.716000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.6715</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8667</v>
+        <v>1.3088</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0955</v>
+        <v>0.2106</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.0983</v>
       </c>
       <c r="G13" t="n">
         <v>0.5507</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4591</v>
+        <v>-0.017</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0396</v>
+        <v>0.1757</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4151</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6093</v>
+        <v>-0.8284</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7633</v>
+        <v>-0.9274</v>
       </c>
       <c r="F14" t="n">
-        <v>0.154</v>
+        <v>0.0989</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.177</v>
+        <v>-1.884</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4205</v>
+        <v>-1.7946</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1229</v>
+        <v>-0.8364</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.163</v>
+        <v>-0.1963</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0402</v>
+        <v>-0.64</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0542</v>
+        <v>-1.0476</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2574</v>
+        <v>-1.5983</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7967</v>
+        <v>0.5507</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.844</v>
+        <v>-0.3047</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7483</v>
+        <v>-0.357</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0958</v>
+        <v>0.0524</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5253</v>
+        <v>-0.0285</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0779</v>
+        <v>-0.2945</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0388</v>
+        <v>-1.1032</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1744</v>
+        <v>-1.4775</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2132</v>
+        <v>0.3742</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1243</v>
+        <v>-2.177</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4641</v>
+        <v>-1.4205</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5884</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9281</v>
+        <v>-1.1229</v>
       </c>
       <c r="K15" t="n">
-        <v>1.528</v>
+        <v>-1.163</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5999</v>
+        <v>0.0402</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0525</v>
+        <v>-1.0542</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0639</v>
+        <v>-0.2574</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9886</v>
+        <v>-0.7967</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9838</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5729</v>
+        <v>0.35</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7537</v>
+        <v>0.0341</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8191000000000001</v>
+        <v>0.316</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6745</v>
+        <v>0.5253</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6745</v>
+        <v>-0.0779</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2986</v>
+        <v>-1.2046</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2335</v>
+        <v>-0.1317</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-1.0729</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.884</v>
+        <v>-2.1243</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7946</v>
+        <v>0.4641</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-2.5884</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8364</v>
+        <v>0.9281</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1963</v>
+        <v>1.528</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.64</v>
+        <v>-0.5999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0476</v>
+        <v>-3.0525</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5983</v>
+        <v>-1.0639</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5507</v>
+        <v>-1.9886</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7748</v>
+        <v>-1.7387</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6631</v>
+        <v>-1.0598</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1117</v>
+        <v>-0.6788</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0285</v>
+        <v>0.6745</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2945</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.207</v>
+        <v>-2.4034</v>
       </c>
       <c r="E17" t="n">
         <v>-1.594</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.613</v>
+        <v>-0.8094</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5407999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1342</v>
+        <v>-1.3306</v>
       </c>
       <c r="T17" t="n">
         <v>-0.9862</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.148</v>
+        <v>-0.3444</v>
       </c>
       <c r="V17" t="n">
         <v>-0.532</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1956</v>
+        <v>-2.711</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9593</v>
+        <v>-0.7552</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2363</v>
+        <v>-1.9557</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9155</v>
@@ -1858,13 +1858,13 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.3352</v>
+        <v>-1.8506</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2979</v>
+        <v>-1.0938</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0373</v>
+        <v>-0.7568</v>
       </c>
       <c r="V18" t="n">
         <v>0.0713</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2382</v>
+        <v>-3.4142</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0801</v>
+        <v>-1.2842</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1581</v>
+        <v>-2.1301</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3529</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2307</v>
+        <v>-0.4067</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1928</v>
+        <v>-0.0113</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4235</v>
+        <v>-0.3954</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6966</v>
+        <v>-4.0931</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4441</v>
+        <v>-4.3322</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2525</v>
+        <v>0.2391</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2374</v>
+        <v>-2.7778</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0406</v>
+        <v>-1.6779</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1969</v>
+        <v>-1.0999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4757</v>
+        <v>-0.999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2281</v>
+        <v>-0.2812</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2476</v>
+        <v>-0.7178</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.7131</v>
+        <v>-1.7788</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2687</v>
+        <v>-1.3967</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4444</v>
+        <v>-0.3821</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7369</v>
+        <v>-0.7694</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5473</v>
+        <v>-0.6234</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8103</v>
+        <v>-0.146</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0713</v>
+        <v>-0.1492</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>-0.4151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2061</v>
+        <v>-4.4363</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9444</v>
+        <v>-2.3421</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2617</v>
+        <v>-2.0942</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7778</v>
+        <v>-2.2374</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6779</v>
+        <v>-2.0406</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0999</v>
+        <v>-0.1969</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.999</v>
+        <v>1.4757</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2812</v>
+        <v>0.2281</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7178</v>
+        <v>1.2476</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7788</v>
+        <v>-3.7131</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3967</v>
+        <v>-2.2687</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3821</v>
+        <v>-1.4444</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>2.579</v>
+        <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8823</v>
+        <v>-1.4766</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2356</v>
+        <v>-1.4452</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6468</v>
+        <v>-0.0313</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1492</v>
+        <v>0.0713</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4151</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1026</v>
+        <v>-6.543</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0636</v>
+        <v>-4.4717</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.039</v>
+        <v>-2.0713</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8303</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4206</v>
+        <v>-0.0198</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3119</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1087</v>
+        <v>0.0764</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2961</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9538</v>
+        <v>-6.5712</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.66</v>
+        <v>-2.558</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2938</v>
+        <v>-4.0132</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9376</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8874</v>
+        <v>-1.5049</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9862</v>
+        <v>-0.8841</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9013</v>
+        <v>-0.6207</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3271</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.6799</v>
+        <v>-31.9996</v>
       </c>
       <c r="E24" t="n">
         <v>-19.6634</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.0165</v>
+        <v>-12.3363</v>
       </c>
       <c r="G24" t="n">
         <v>-23.2269</v>
@@ -2326,13 +2326,13 @@
         <v>17.8545</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.748900000000001</v>
+        <v>-9.068999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.7158</v>
+        <v>-6.7156</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.033300000000001</v>
+        <v>-2.3529</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6716</v>
@@ -2341,7 +2341,7 @@
         <v>1.3299</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.001399999999999</v>
+        <v>-5.0014</v>
       </c>
     </row>
   </sheetData>
